--- a/KAMCHATKA_ZAPOLNENIE/04_ООО_Сибирский_завод_трубопроводной_армат.xlsx
+++ b/KAMCHATKA_ZAPOLNENIE/04_ООО_Сибирский_завод_трубопроводной_армат.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -598,7 +598,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+          <t>Графы марка / производитель / страна / № записи частично ПРЕДЗАПОЛНЕНЫ нами по вашему КП и открытым данным — проверьте и исправьте, если не так.</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -632,289 +632,222 @@
       <c r="AD3" s="2" t="n"/>
       <c r="AE3" s="2" t="n"/>
     </row>
-    <row r="4" ht="66" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Нацрежим ПП 1875 (ограничение): обязательны производитель, страна и ДЕЙСТВУЮЩИЙ номер реестровой записи ПП 719 (для ЕАЭС — евразийский реестр). Приложите выписку из ГИСП и сертификаты. Доставка — до Петропавловска-Камчатского (укажите вес).</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
+      <c r="U4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
+      <c r="AA4" s="2" t="n"/>
+      <c r="AB4" s="2" t="n"/>
+      <c r="AC4" s="2" t="n"/>
+      <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Табл./№ ТЗ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ГОСТ/ТУ</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Ду, мм</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Проход</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Давление, МПа</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Температура, °С</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Среда</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Материал корпуса</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Климатическое исполнение</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Присоединение</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: наименование</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Приводное устройство: технические характеристики</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>Установочное положение</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>Материал штока, шара, уплотнений</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>Габариты</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U5" s="4" t="inlineStr">
         <is>
           <t>Предлагаемая марка / обозначение</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="V5" s="4" t="inlineStr">
         <is>
           <t>Производитель (завод)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>Страна происхождения</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>№ реестровой записи (ПП 719) или евразийского реестра</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Срок действия записи</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Соответствие ТЗ: «да» или отличия</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Цена за ед. с НДС, ₽</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>Сумма с НДС, ₽</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>Срок отгрузки</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AD5" s="4" t="inlineStr">
         <is>
           <t>Вес ед., кг / габариты</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>Сертификат / декларация ТР ТС №</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>1.1/11</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Задвижка 30С576НЖ Ду 300 Ру 63 с редуктором РК-Г-1М, в комплекте с крепежом и ответными фланцами.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>ГОСТ 9544-2015</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>стандарт</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>6.3</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>до +425</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>жидкие и газообразные углеводороды, нефть, нефтепродукты, природный газ, газоконденсат, вода, пар, а так же другие агрессивные жидкости и газы, неагрессивные к примененным в задвижке клиновой материалам</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Сталь 25Л</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>У1</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>фланец -фланец под приварку</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>редуктор РК-Г1</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>РК-Г-1</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>любое</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Корпус: сталь 25Л    Крышка: сталь 25Л Клин: сталь 25Л  Шпиндель: сталь 20Х13     Гайка шпинделя: латунь ЛС59    Гайка: сталь 45     Шпилька, болт: сталь 35ХМ     . Болт откидной: сталь 35ХМ      Прокладка: спирально-навитая     • 10. Набивка сальника: ТРГ     • 11. Редуктор: редуктор конический или цилиндрический     • 12. Подшипник: по ГОСТ 7872-89     • 13. Наплавка на кольце в корпусе: сталь 07Х25Н13   Наплавка на клине: сталь 13Х25Т</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
-      <c r="X5" s="7" t="n"/>
-      <c r="Y5" s="7" t="n"/>
-      <c r="Z5" s="7" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9">
-        <f>AA5*S5</f>
-        <v/>
-      </c>
-      <c r="AC5" s="7" t="n"/>
-      <c r="AD5" s="7" t="n"/>
-      <c r="AE5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>1.3/78</t>
+          <t>1.1/11</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
+          <t>Задвижка 30С576НЖ Ду 300 Ру 63 с редуктором РК-Г-1М, в комплекте с крепежом и ответными фланцами.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>ГОСТ 5762-2002</t>
+          <t>ГОСТ 9544-2015</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -924,22 +857,22 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>от −40°С  до +425°С</t>
+          <t>до +425</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>вода, пар, неагрессивные нефтепродукты</t>
+          <t>жидкие и газообразные углеводороды, нефть, нефтепродукты, природный газ, газоконденсат, вода, пар, а так же другие агрессивные жидкости и газы, неагрессивные к примененным в задвижке клиновой материалам</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>сталь 25л</t>
+          <t>Сталь 25Л</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -949,33 +882,33 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>фланцевый</t>
+          <t>фланец -фланец под приварку</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>ручной</t>
+          <t>редуктор РК-Г1</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>маховик</t>
+          <t>РК-Г-1</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
         <is>
-          <t>горизонтальное, либо вертикальное</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>Крышка, клин Ст25Л, шпиндель Ст20х13</t>
+          <t>Корпус: сталь 25Л    Крышка: сталь 25Л Клин: сталь 25Л  Шпиндель: сталь 20Х13     Гайка шпинделя: латунь ЛС59    Гайка: сталь 45     Шпилька, болт: сталь 35ХМ     . Болт откидной: сталь 35ХМ      Прокладка: спирально-навитая     • 10. Набивка сальника: ТРГ     • 11. Редуктор: редуктор конический или цилиндрический     • 12. Подшипник: по ГОСТ 7872-89     • 13. Наплавка на кольце в корпусе: сталь 07Х25Н13   Наплавка на клине: сталь 13Х25Т</t>
         </is>
       </c>
       <c r="Q6" s="6" t="inlineStr"/>
       <c r="R6" s="6" t="inlineStr"/>
       <c r="S6" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
@@ -999,16 +932,16 @@
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1.3/79</t>
+          <t>1.3/78</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1018,7 +951,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1079,7 +1012,7 @@
       <c r="Q7" s="6" t="inlineStr"/>
       <c r="R7" s="6" t="inlineStr"/>
       <c r="S7" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
@@ -1103,16 +1036,16 @@
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>1.3/80</t>
+          <t>1.3/79</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 100 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1122,7 +1055,7 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -1183,7 +1116,7 @@
       <c r="Q8" s="6" t="inlineStr"/>
       <c r="R8" s="6" t="inlineStr"/>
       <c r="S8" s="5" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
@@ -1207,16 +1140,16 @@
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>1.3/81</t>
+          <t>1.3/80</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 150 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 100 Ру 25</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1226,7 +1159,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -1287,7 +1220,7 @@
       <c r="Q9" s="6" t="inlineStr"/>
       <c r="R9" s="6" t="inlineStr"/>
       <c r="S9" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
@@ -1311,16 +1244,16 @@
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1.3/82</t>
+          <t>1.3/81</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 200 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 150 Ру 25</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -1330,7 +1263,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1345,54 +1278,53 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>-40…        +425</t>
+          <t>от −40°С  до +425°С</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Вода, воздух, пар, аммиак,природный газ, нефть,нефтепродукты</t>
+          <t>вода, пар, неагрессивные нефтепродукты</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>сталь 25Л</t>
+          <t>сталь 25л</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Условия эксплуатации У
-Минимальная температура окружающего воздуха: −40°С</t>
+          <t>У1</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>фланец-фланец</t>
+          <t>фланцевый</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>Ручное</t>
+          <t>ручной</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>Маховик</t>
+          <t>маховик</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>Вертикально маховиком вверх, горизонтально</t>
+          <t>горизонтальное, либо вертикальное</t>
         </is>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>С КОФ. Корпус, клин, крышка, маховик -  только сталь 20Л или 25Л,  шпиндель - сталь 20Х13, наплавка на кольце в корпусе и наплавка на клине 07Х25Н13 или схожая по свойствам, прокладка и сальниковое уплотнение только ТРГ</t>
+          <t>Крышка, клин Ст25Л, шпиндель Ст20х13</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr"/>
       <c r="R10" s="6" t="inlineStr"/>
       <c r="S10" s="5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
@@ -1416,16 +1348,16 @@
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1.3/83</t>
+          <t>1.3/82</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 250 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 200 Ру 25</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1435,7 +1367,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -1450,12 +1382,12 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>до +425</t>
+          <t>-40…        +425</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>вода, пар, нефть, природный газ, жидкие и газообразные неагрессивные нефтепродукты</t>
+          <t>Вода, воздух, пар, аммиак,природный газ, нефть,нефтепродукты</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -1465,17 +1397,18 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>У1</t>
+          <t>Условия эксплуатации У
+Минимальная температура окружающего воздуха: −40°С</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>фланцевый</t>
+          <t>фланец-фланец</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>ручной</t>
+          <t>Ручное</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
@@ -1485,18 +1418,18 @@
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>любое, кроме маховиком вниз</t>
+          <t>Вертикально маховиком вверх, горизонтально</t>
         </is>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Корпус, Крышка, Клин, Маховик - Сталь 25Л Шпиндель - Сталь 20Х13 Прокладка и уплотнение - ТРГ Наплавка на кольце в корпусе и на клине - Сталь 20Х13</t>
+          <t>С КОФ. Корпус, клин, крышка, маховик -  только сталь 20Л или 25Л,  шпиндель - сталь 20Х13, наплавка на кольце в корпусе и наплавка на клине 07Х25Н13 или схожая по свойствам, прокладка и сальниковое уплотнение только ТРГ</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr"/>
       <c r="R11" s="6" t="inlineStr"/>
       <c r="S11" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
@@ -1520,16 +1453,16 @@
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>1.3/84</t>
+          <t>1.3/83</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 300 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 250 Ру 25</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1539,7 +1472,7 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>250</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -1579,12 +1512,12 @@
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>ручной (маховик)</t>
+          <t>ручной</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Маховик</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
@@ -1600,7 +1533,7 @@
       <c r="Q12" s="6" t="inlineStr"/>
       <c r="R12" s="6" t="inlineStr"/>
       <c r="S12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
@@ -1624,16 +1557,16 @@
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>1.5/2</t>
+          <t>1.3/84</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 300 Ру 25</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -1643,7 +1576,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>300</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -1658,17 +1591,17 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>от −40°С  до +425°С</t>
+          <t>до +425</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>вода, пар, неагрессивные нефтепродукты</t>
+          <t>вода, пар, нефть, природный газ, жидкие и газообразные неагрессивные нефтепродукты</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>сталь 25л</t>
+          <t>сталь 25Л</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1683,28 +1616,28 @@
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>ручной</t>
+          <t>ручной (маховик)</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>маховик</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>горизонтальное, либо вертикальное</t>
+          <t>любое, кроме маховиком вниз</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Крышка, клин Ст25Л, шпиндель Ст20х13</t>
+          <t>Корпус, Крышка, Клин, Маховик - Сталь 25Л Шпиндель - Сталь 20Х13 Прокладка и уплотнение - ТРГ Наплавка на кольце в корпусе и на клине - Сталь 20Х13</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr"/>
       <c r="R13" s="6" t="inlineStr"/>
       <c r="S13" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
@@ -1728,16 +1661,16 @@
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>1.5/3</t>
+          <t>1.5/2</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
+          <t>Задвижка 30с64нж Ду 50 Ру 25</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -1747,7 +1680,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1831,44 +1764,148 @@
       <c r="AE14" s="7" t="n"/>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr"/>
-      <c r="B15" s="10" t="inlineStr"/>
-      <c r="C15" s="10" t="inlineStr"/>
-      <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="10" t="inlineStr"/>
-      <c r="F15" s="10" t="inlineStr"/>
-      <c r="G15" s="10" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr"/>
-      <c r="I15" s="10" t="inlineStr"/>
-      <c r="J15" s="10" t="inlineStr"/>
-      <c r="K15" s="10" t="inlineStr"/>
-      <c r="L15" s="10" t="inlineStr"/>
-      <c r="M15" s="10" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
-      <c r="O15" s="10" t="inlineStr"/>
-      <c r="P15" s="10" t="inlineStr"/>
-      <c r="Q15" s="10" t="inlineStr"/>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="10" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr"/>
-      <c r="V15" s="10" t="inlineStr"/>
-      <c r="W15" s="10" t="inlineStr"/>
-      <c r="X15" s="10" t="inlineStr"/>
-      <c r="Y15" s="10" t="inlineStr"/>
-      <c r="Z15" s="10" t="inlineStr"/>
-      <c r="AA15" s="10" t="inlineStr">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>1.5/3</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Задвижка 30с64нж Ду 80 Ру 25</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>ГОСТ 5762-2002</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>стандарт</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>от −40°С  до +425°С</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>вода, пар, неагрессивные нефтепродукты</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>сталь 25л</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>У1</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>фланцевый</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>ручной</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>маховик</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>горизонтальное, либо вертикальное</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Крышка, клин Ст25Л, шпиндель Ст20х13</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr"/>
+      <c r="S15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="U15" s="7" t="n"/>
+      <c r="V15" s="7" t="n"/>
+      <c r="W15" s="7" t="n"/>
+      <c r="X15" s="7" t="n"/>
+      <c r="Y15" s="7" t="n"/>
+      <c r="Z15" s="7" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="9">
+        <f>AA15*S15</f>
+        <v/>
+      </c>
+      <c r="AC15" s="7" t="n"/>
+      <c r="AD15" s="7" t="n"/>
+      <c r="AE15" s="7" t="n"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="10" t="inlineStr"/>
+      <c r="B16" s="10" t="inlineStr"/>
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="inlineStr"/>
+      <c r="J16" s="10" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr"/>
+      <c r="L16" s="10" t="inlineStr"/>
+      <c r="M16" s="10" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
+      <c r="O16" s="10" t="inlineStr"/>
+      <c r="P16" s="10" t="inlineStr"/>
+      <c r="Q16" s="10" t="inlineStr"/>
+      <c r="R16" s="10" t="inlineStr"/>
+      <c r="S16" s="10" t="inlineStr"/>
+      <c r="T16" s="10" t="inlineStr"/>
+      <c r="U16" s="10" t="inlineStr"/>
+      <c r="V16" s="10" t="inlineStr"/>
+      <c r="W16" s="10" t="inlineStr"/>
+      <c r="X16" s="10" t="inlineStr"/>
+      <c r="Y16" s="10" t="inlineStr"/>
+      <c r="Z16" s="10" t="inlineStr"/>
+      <c r="AA16" s="10" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="AB15" s="11">
-        <f>SUM(AB5:AB14)</f>
+      <c r="AB16" s="11">
+        <f>SUM(AB6:AB15)</f>
         <v/>
       </c>
-      <c r="AC15" s="2" t="n"/>
-      <c r="AD15" s="2" t="n"/>
-      <c r="AE15" s="2" t="n"/>
+      <c r="AC16" s="2" t="n"/>
+      <c r="AD16" s="2" t="n"/>
+      <c r="AE16" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
